--- a/data/trans_orig/MCS12_SP_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los cuartiles de la puntuación del componente de salud mental (SF12) en 2007</t>
+          <t>Población según la puntuación, en cuartiles, del componente de salud mental (SF12) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>181221</t>
+          <t>181800</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>232444</t>
+          <t>231592</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>211586</t>
+          <t>212961</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>269269</t>
+          <t>268570</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>407541</t>
+          <t>410222</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>485265</t>
+          <t>481014</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>255652</t>
+          <t>254705</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>314130</t>
+          <t>314039</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>309576</t>
+          <t>307453</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>371989</t>
+          <t>370311</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>583074</t>
+          <t>582897</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>666254</t>
+          <t>666788</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>236468</t>
+          <t>232920</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>291542</t>
+          <t>289141</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>277965</t>
+          <t>277154</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>337389</t>
+          <t>335704</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>526578</t>
+          <t>528014</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>610819</t>
+          <t>612064</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>248599</t>
+          <t>248336</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>307953</t>
+          <t>308419</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>398776</t>
+          <t>397033</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>465179</t>
+          <t>463049</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>666079</t>
+          <t>664875</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>756787</t>
+          <t>752621</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>388051</t>
+          <t>390474</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>459844</t>
+          <t>457949</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>202241</t>
+          <t>200235</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>257326</t>
+          <t>257048</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>609509</t>
+          <t>608381</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>699139</t>
+          <t>698871</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>568030</t>
+          <t>573143</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>648164</t>
+          <t>653001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>479616</t>
+          <t>482376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>555850</t>
+          <t>556852</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1068246</t>
+          <t>1076601</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1180407</t>
+          <t>1188753</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>376898</t>
+          <t>375954</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>448087</t>
+          <t>448867</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>442115</t>
+          <t>441220</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>511485</t>
+          <t>515566</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>841627</t>
+          <t>837634</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>942480</t>
+          <t>940328</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>217485</t>
+          <t>220603</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>279147</t>
+          <t>279499</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>329270</t>
+          <t>332221</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>394601</t>
+          <t>398073</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>566086</t>
+          <t>563412</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>656310</t>
+          <t>654068</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>125209</t>
+          <t>125077</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168009</t>
+          <t>165772</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58006</t>
+          <t>59113</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>90821</t>
+          <t>91195</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>192833</t>
+          <t>192506</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>245151</t>
+          <t>247268</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>168649</t>
+          <t>167375</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>214284</t>
+          <t>211863</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>129926</t>
+          <t>129511</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>171365</t>
+          <t>170127</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>307258</t>
+          <t>309304</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>371845</t>
+          <t>370811</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,08%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>113136</t>
+          <t>112515</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>150999</t>
+          <t>155088</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>130019</t>
+          <t>129849</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>169172</t>
+          <t>170539</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>251903</t>
+          <t>252813</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>309083</t>
+          <t>308864</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67267</t>
+          <t>68451</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101454</t>
+          <t>104107</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>85104</t>
+          <t>87329</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>121412</t>
+          <t>123184</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>164615</t>
+          <t>161675</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>216566</t>
+          <t>212846</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>724972</t>
+          <t>722984</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>827270</t>
+          <t>825487</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>500866</t>
+          <t>497269</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>585130</t>
+          <t>587058</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1258318</t>
+          <t>1255085</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1382744</t>
+          <t>1380323</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1030978</t>
+          <t>1031605</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1138874</t>
+          <t>1138358</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>947484</t>
+          <t>950043</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1059407</t>
+          <t>1056859</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2022030</t>
+          <t>2019315</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2168851</t>
+          <t>2170910</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>758238</t>
+          <t>760825</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>853392</t>
+          <t>859548</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>886066</t>
+          <t>885793</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>985180</t>
+          <t>986774</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1671549</t>
+          <t>1666734</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1812193</t>
+          <t>1808574</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>567515</t>
+          <t>570263</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>656212</t>
+          <t>662516</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>841377</t>
+          <t>846053</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>950929</t>
+          <t>947894</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1444252</t>
+          <t>1446647</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1579259</t>
+          <t>1569483</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los cuartiles de la puntuación del componente de salud mental (SF12) en 2012</t>
+          <t>Población según la puntuación, en cuartiles, del componente de salud mental (SF12) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>217486</t>
+          <t>217916</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>273634</t>
+          <t>274720</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>227207</t>
+          <t>227284</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>284208</t>
+          <t>283834</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>459950</t>
+          <t>461814</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>540830</t>
+          <t>542684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>173848</t>
+          <t>171822</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>224241</t>
+          <t>223384</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>157308</t>
+          <t>157544</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>212313</t>
+          <t>210967</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>346750</t>
+          <t>346610</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>419107</t>
+          <t>422281</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>215215</t>
+          <t>215451</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>268887</t>
+          <t>271584</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>333402</t>
+          <t>332438</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>398318</t>
+          <t>397351</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>567506</t>
+          <t>558310</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>653300</t>
+          <t>647994</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>261470</t>
+          <t>262387</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>320983</t>
+          <t>320980</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>493181</t>
+          <t>496352</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>568835</t>
+          <t>569776</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>778259</t>
+          <t>774411</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>876591</t>
+          <t>873842</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,79%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>558311</t>
+          <t>554341</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>640189</t>
+          <t>639627</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>360198</t>
+          <t>362128</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>425633</t>
+          <t>430458</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>931131</t>
+          <t>931760</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1046470</t>
+          <t>1045355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>402320</t>
+          <t>405041</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>481131</t>
+          <t>480527</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>285258</t>
+          <t>283913</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>351600</t>
+          <t>350479</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>706578</t>
+          <t>702793</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>809378</t>
+          <t>808039</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>476246</t>
+          <t>477174</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>560071</t>
+          <t>557512</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>477411</t>
+          <t>478769</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>557451</t>
+          <t>559957</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>978570</t>
+          <t>978667</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1092760</t>
+          <t>1089957</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>374497</t>
+          <t>373510</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>448089</t>
+          <t>445839</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>493370</t>
+          <t>492373</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>570787</t>
+          <t>574047</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>881911</t>
+          <t>884212</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>989941</t>
+          <t>994018</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132516</t>
+          <t>130528</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>176965</t>
+          <t>175135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>105594</t>
+          <t>104491</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>145965</t>
+          <t>144734</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>251162</t>
+          <t>248835</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>312424</t>
+          <t>304833</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91592</t>
+          <t>93558</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>131303</t>
+          <t>132823</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>68189</t>
+          <t>70350</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>104989</t>
+          <t>104703</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>169939</t>
+          <t>173704</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>222335</t>
+          <t>223457</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>132643</t>
+          <t>133495</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>177944</t>
+          <t>177870</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>133751</t>
+          <t>134424</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>176583</t>
+          <t>176897</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>278782</t>
+          <t>280391</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>341342</t>
+          <t>340230</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,2%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47147</t>
+          <t>47403</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78772</t>
+          <t>81641</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>77891</t>
+          <t>78133</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>115665</t>
+          <t>114467</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>132249</t>
+          <t>131933</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>183040</t>
+          <t>180647</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>942243</t>
+          <t>943914</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1049386</t>
+          <t>1050586</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>720272</t>
+          <t>720308</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>822225</t>
+          <t>822037</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1694194</t>
+          <t>1693481</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1848132</t>
+          <t>1838570</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>700005</t>
+          <t>706685</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>802829</t>
+          <t>800186</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>540442</t>
+          <t>545550</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>634543</t>
+          <t>631710</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1271466</t>
+          <t>1270438</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1405451</t>
+          <t>1407894</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>857272</t>
+          <t>859239</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>963655</t>
+          <t>965401</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>984143</t>
+          <t>978591</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1095587</t>
+          <t>1092761</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1864475</t>
+          <t>1875412</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2023549</t>
+          <t>2029309</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>706802</t>
+          <t>713591</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>814552</t>
+          <t>808296</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1104075</t>
+          <t>1107804</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1216226</t>
+          <t>1218321</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1834592</t>
+          <t>1851098</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1999486</t>
+          <t>2000397</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los cuartiles de la puntuación del componente de salud mental (SF12) en 2016</t>
+          <t>Población según la puntuación, en cuartiles, del componente de salud mental (SF12) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>161781</t>
+          <t>161682</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>207900</t>
+          <t>206367</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>196312</t>
+          <t>193825</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>251246</t>
+          <t>251457</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>366495</t>
+          <t>366387</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>441068</t>
+          <t>436291</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,95%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>125894</t>
+          <t>126930</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>167454</t>
+          <t>166997</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>138670</t>
+          <t>135955</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186053</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>275048</t>
+          <t>274124</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>339490</t>
+          <t>335374</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>201968</t>
+          <t>204574</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>253984</t>
+          <t>253414</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>202923</t>
+          <t>201672</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>258104</t>
+          <t>258237</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>419000</t>
+          <t>419863</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>493499</t>
+          <t>493701</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>172472</t>
+          <t>173321</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>220755</t>
+          <t>221758</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>351446</t>
+          <t>351995</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>416848</t>
+          <t>418077</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>543277</t>
+          <t>544710</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>623150</t>
+          <t>622898</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>573580</t>
+          <t>572477</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>662033</t>
+          <t>660005</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>474686</t>
+          <t>473056</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>554873</t>
+          <t>550928</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1074899</t>
+          <t>1075805</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1192818</t>
+          <t>1189519</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>464343</t>
+          <t>462148</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>544614</t>
+          <t>540385</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>391757</t>
+          <t>392254</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>464878</t>
+          <t>466177</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>879237</t>
+          <t>880718</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>987968</t>
+          <t>992295</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>556523</t>
+          <t>557170</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>641688</t>
+          <t>640416</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>555713</t>
+          <t>551530</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>635618</t>
+          <t>634239</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1137485</t>
+          <t>1133157</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1256022</t>
+          <t>1255041</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>321547</t>
+          <t>325245</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>390872</t>
+          <t>394070</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>413050</t>
+          <t>416332</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>487893</t>
+          <t>492101</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>757817</t>
+          <t>756741</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>861777</t>
+          <t>857813</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134208</t>
+          <t>133113</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>179057</t>
+          <t>176928</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>116595</t>
+          <t>116290</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157806</t>
+          <t>157010</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260719</t>
+          <t>262612</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>322599</t>
+          <t>320040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>126772</t>
+          <t>123794</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>168426</t>
+          <t>167322</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>114085</t>
+          <t>114714</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>157610</t>
+          <t>156882</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>252476</t>
+          <t>252293</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>313383</t>
+          <t>311929</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,46%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139464</t>
+          <t>139544</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>185969</t>
+          <t>183559</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>146462</t>
+          <t>145075</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>190704</t>
+          <t>192244</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>299496</t>
+          <t>298622</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>361363</t>
+          <t>364864</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67473</t>
+          <t>68540</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102944</t>
+          <t>104954</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89977</t>
+          <t>92457</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>127833</t>
+          <t>129306</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>167326</t>
+          <t>169809</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>222951</t>
+          <t>219379</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>904152</t>
+          <t>906891</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1012075</t>
+          <t>1017786</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>820599</t>
+          <t>817839</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>923460</t>
+          <t>930322</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1753072</t>
+          <t>1749749</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1905443</t>
+          <t>1901823</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>746862</t>
+          <t>745033</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>852480</t>
+          <t>842145</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>678948</t>
+          <t>677531</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>777081</t>
+          <t>777676</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1455487</t>
+          <t>1449960</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1598767</t>
+          <t>1594099</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>936278</t>
+          <t>930345</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1045722</t>
+          <t>1037603</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>936821</t>
+          <t>935706</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1047183</t>
+          <t>1046609</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1901549</t>
+          <t>1900209</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2058084</t>
+          <t>2061386</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>593074</t>
+          <t>589727</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>683772</t>
+          <t>680803</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>894366</t>
+          <t>893884</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>996855</t>
+          <t>1002706</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1510508</t>
+          <t>1510140</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1658548</t>
+          <t>1655647</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los cuartiles de la puntuación del componente de salud mental (SF12) en 2023</t>
+          <t>Población según la puntuación, en cuartiles, del componente de salud mental (SF12) en 2023 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>114482</t>
+          <t>114326</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>150345</t>
+          <t>151132</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>146840</t>
+          <t>148562</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>183740</t>
+          <t>185555</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>272111</t>
+          <t>273640</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>322094</t>
+          <t>325602</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98009</t>
+          <t>96606</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132341</t>
+          <t>131111</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>104639</t>
+          <t>104418</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>134172</t>
+          <t>134091</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>211533</t>
+          <t>212459</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>255982</t>
+          <t>257495</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>105914</t>
+          <t>105656</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>144362</t>
+          <t>143308</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>151581</t>
+          <t>150419</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>185347</t>
+          <t>184525</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>263323</t>
+          <t>265388</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>317566</t>
+          <t>316167</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>123137</t>
+          <t>123327</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>159298</t>
+          <t>158964</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>272733</t>
+          <t>274644</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>316786</t>
+          <t>316576</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>409406</t>
+          <t>405065</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>466284</t>
+          <t>463790</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,93%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>499347</t>
+          <t>482962</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>826416</t>
+          <t>825944</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>428647</t>
+          <t>434643</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>688273</t>
+          <t>684720</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1049453</t>
+          <t>1067288</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1454003</t>
+          <t>1461819</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>560115</t>
+          <t>562805</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1219820</t>
+          <t>1254564</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>338006</t>
+          <t>340907</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>540981</t>
+          <t>536207</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>999171</t>
+          <t>1005518</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1891458</t>
+          <t>1766830</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>39,14%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304541</t>
+          <t>300356</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>510643</t>
+          <t>505036</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>380801</t>
+          <t>392999</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>671329</t>
+          <t>672411</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>786526</t>
+          <t>775704</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1129799</t>
+          <t>1114692</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>253798</t>
+          <t>252404</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>422309</t>
+          <t>426905</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>498251</t>
+          <t>503550</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1109636</t>
+          <t>1105347</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>826810</t>
+          <t>841011</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1587829</t>
+          <t>1663904</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>183318</t>
+          <t>181037</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>233945</t>
+          <t>234246</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>160557</t>
+          <t>161861</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>201278</t>
+          <t>202965</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>353486</t>
+          <t>357361</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>420577</t>
+          <t>423107</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,5%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>150275</t>
+          <t>149842</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>200345</t>
+          <t>200049</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>143138</t>
+          <t>143155</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181909</t>
+          <t>181283</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>307373</t>
+          <t>304001</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>368532</t>
+          <t>367007</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>119836</t>
+          <t>117237</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>161333</t>
+          <t>158263</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>139920</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>178517</t>
+          <t>177170</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>270745</t>
+          <t>271153</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>328628</t>
+          <t>331181</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105841</t>
+          <t>105665</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154174</t>
+          <t>158954</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>138747</t>
+          <t>135953</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>176259</t>
+          <t>174573</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>251549</t>
+          <t>251187</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>313387</t>
+          <t>314116</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>823049</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1160908</t>
+          <t>1163278</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>757596</t>
+          <t>767965</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1020408</t>
+          <t>1022377</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1724000</t>
+          <t>1712828</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2149386</t>
+          <t>2139365</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>850357</t>
+          <t>846984</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1639791</t>
+          <t>1624791</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>610932</t>
+          <t>603633</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>819254</t>
+          <t>816437</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1575014</t>
+          <t>1565431</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2440455</t>
+          <t>2388231</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>519896</t>
+          <t>552828</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>768952</t>
+          <t>772338</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>705464</t>
+          <t>700070</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>990138</t>
+          <t>980813</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1342249</t>
+          <t>1339952</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1729706</t>
+          <t>1715907</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>484412</t>
+          <t>502703</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>697826</t>
+          <t>701798</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>956133</t>
+          <t>962254</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1709159</t>
+          <t>1580570</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1550992</t>
+          <t>1543718</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2300462</t>
+          <t>2406317</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/MCS12_SP_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>181800</t>
+          <t>183587</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>231592</t>
+          <t>233001</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>212961</t>
+          <t>211226</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>268570</t>
+          <t>267178</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>410222</t>
+          <t>407466</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>481014</t>
+          <t>483964</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>254705</t>
+          <t>254687</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>314039</t>
+          <t>313276</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307453</t>
+          <t>309619</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>370311</t>
+          <t>368765</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>582897</t>
+          <t>579313</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>666788</t>
+          <t>667868</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,46%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>232920</t>
+          <t>233339</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>289141</t>
+          <t>292245</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>277154</t>
+          <t>277434</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>335704</t>
+          <t>338939</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>528014</t>
+          <t>532543</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>612064</t>
+          <t>613338</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>248336</t>
+          <t>251759</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>308419</t>
+          <t>309768</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>397033</t>
+          <t>397483</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>463049</t>
+          <t>465087</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>664875</t>
+          <t>662394</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>752621</t>
+          <t>753629</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>390474</t>
+          <t>387959</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>457949</t>
+          <t>461915</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>200235</t>
+          <t>201662</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>257048</t>
+          <t>258298</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>608381</t>
+          <t>611805</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>698871</t>
+          <t>698018</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>573143</t>
+          <t>571439</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>653001</t>
+          <t>653906</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>482376</t>
+          <t>480691</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>556852</t>
+          <t>555442</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1076601</t>
+          <t>1070260</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1188753</t>
+          <t>1182365</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,04%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>375954</t>
+          <t>377279</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>448867</t>
+          <t>449968</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>441220</t>
+          <t>441026</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>515566</t>
+          <t>517009</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>837634</t>
+          <t>839196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>940328</t>
+          <t>943790</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>220603</t>
+          <t>219251</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>279499</t>
+          <t>276572</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>332221</t>
+          <t>330078</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>398073</t>
+          <t>400513</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>563412</t>
+          <t>565637</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>654068</t>
+          <t>656515</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>125077</t>
+          <t>124378</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>165772</t>
+          <t>166197</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59113</t>
+          <t>59565</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91195</t>
+          <t>91461</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>192506</t>
+          <t>192417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>247268</t>
+          <t>246028</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>167375</t>
+          <t>166629</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>211863</t>
+          <t>214813</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>129511</t>
+          <t>127125</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>170127</t>
+          <t>170269</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>309304</t>
+          <t>311701</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>370811</t>
+          <t>370400</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,04%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>112515</t>
+          <t>112521</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>155088</t>
+          <t>155286</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>129849</t>
+          <t>129028</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>170539</t>
+          <t>168623</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>252813</t>
+          <t>250742</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>308864</t>
+          <t>312586</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68451</t>
+          <t>68673</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104107</t>
+          <t>102556</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87329</t>
+          <t>86904</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>123184</t>
+          <t>124909</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>161675</t>
+          <t>165357</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>212846</t>
+          <t>220549</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>722984</t>
+          <t>729715</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>825487</t>
+          <t>826753</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>497269</t>
+          <t>498058</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>587058</t>
+          <t>587192</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1255085</t>
+          <t>1252318</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1380323</t>
+          <t>1386048</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1031605</t>
+          <t>1033645</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1138358</t>
+          <t>1142457</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>950043</t>
+          <t>952975</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1056859</t>
+          <t>1059480</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2019315</t>
+          <t>2010344</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2170910</t>
+          <t>2170799</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>760825</t>
+          <t>755048</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>859548</t>
+          <t>850736</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>885793</t>
+          <t>879737</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>986774</t>
+          <t>992152</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1666734</t>
+          <t>1665563</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1808574</t>
+          <t>1815606</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>570263</t>
+          <t>566182</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>662516</t>
+          <t>653942</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>846053</t>
+          <t>846234</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>947894</t>
+          <t>944763</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1446647</t>
+          <t>1441934</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1569483</t>
+          <t>1573020</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>217916</t>
+          <t>218145</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>274720</t>
+          <t>274551</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>227284</t>
+          <t>225285</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>283834</t>
+          <t>285106</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>461814</t>
+          <t>460026</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>542684</t>
+          <t>542334</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>171822</t>
+          <t>173567</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>223384</t>
+          <t>225497</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>157544</t>
+          <t>160663</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>210967</t>
+          <t>212460</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>346610</t>
+          <t>343199</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>422281</t>
+          <t>419002</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>215451</t>
+          <t>213403</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>271584</t>
+          <t>270381</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>332438</t>
+          <t>331096</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>397351</t>
+          <t>397765</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>558310</t>
+          <t>564364</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>647994</t>
+          <t>652191</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>262387</t>
+          <t>260546</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>320980</t>
+          <t>317691</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>496352</t>
+          <t>502104</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>569776</t>
+          <t>571477</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>774411</t>
+          <t>773898</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>873842</t>
+          <t>869997</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,62%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>554341</t>
+          <t>554772</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>639627</t>
+          <t>638714</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>362128</t>
+          <t>357054</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>430458</t>
+          <t>427525</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>931760</t>
+          <t>935395</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1045355</t>
+          <t>1044320</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>405041</t>
+          <t>404149</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>480527</t>
+          <t>480088</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>283913</t>
+          <t>283822</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>350479</t>
+          <t>353421</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>702793</t>
+          <t>707982</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>808039</t>
+          <t>805390</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>477174</t>
+          <t>476914</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>557512</t>
+          <t>559944</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>478769</t>
+          <t>478248</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>559957</t>
+          <t>554016</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>978667</t>
+          <t>979522</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1089957</t>
+          <t>1098257</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>373510</t>
+          <t>372075</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>445839</t>
+          <t>445946</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>492373</t>
+          <t>490086</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>574047</t>
+          <t>568192</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>884212</t>
+          <t>886886</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>994018</t>
+          <t>1000358</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>130528</t>
+          <t>133761</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>175135</t>
+          <t>176764</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>104491</t>
+          <t>103950</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>144734</t>
+          <t>142746</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>248835</t>
+          <t>248346</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>304833</t>
+          <t>307872</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93558</t>
+          <t>93144</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>132823</t>
+          <t>132202</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70350</t>
+          <t>67652</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>104703</t>
+          <t>104307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>173704</t>
+          <t>170254</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>223457</t>
+          <t>225154</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>133495</t>
+          <t>133674</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>177870</t>
+          <t>176968</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>134424</t>
+          <t>136392</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>176897</t>
+          <t>178016</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>280391</t>
+          <t>280094</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>340230</t>
+          <t>342409</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47403</t>
+          <t>47376</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81641</t>
+          <t>79255</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>78133</t>
+          <t>77408</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>114467</t>
+          <t>112922</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>131933</t>
+          <t>133971</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>180647</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>943914</t>
+          <t>938227</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1050586</t>
+          <t>1046515</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>720308</t>
+          <t>721574</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>822037</t>
+          <t>825456</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1693481</t>
+          <t>1696656</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1838570</t>
+          <t>1842351</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>706685</t>
+          <t>700984</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>800186</t>
+          <t>802306</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>545550</t>
+          <t>539540</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>631710</t>
+          <t>632584</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1270438</t>
+          <t>1271379</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1407894</t>
+          <t>1405648</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>859239</t>
+          <t>864023</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>965401</t>
+          <t>970560</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>978591</t>
+          <t>983935</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1092761</t>
+          <t>1096078</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1875412</t>
+          <t>1882068</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2029309</t>
+          <t>2032399</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>713591</t>
+          <t>709609</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>808296</t>
+          <t>811204</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1107804</t>
+          <t>1099379</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1218321</t>
+          <t>1214834</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1851098</t>
+          <t>1843959</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2000397</t>
+          <t>2000238</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>161682</t>
+          <t>160294</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>206367</t>
+          <t>206867</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>193825</t>
+          <t>193404</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>251457</t>
+          <t>248089</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>366387</t>
+          <t>369746</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>436291</t>
+          <t>439984</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>126930</t>
+          <t>126009</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>166997</t>
+          <t>167751</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>135955</t>
+          <t>137701</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>184833</t>
+          <t>183723</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>274124</t>
+          <t>275771</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>335374</t>
+          <t>340773</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>204574</t>
+          <t>203254</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>253414</t>
+          <t>255086</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>201672</t>
+          <t>201651</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>258237</t>
+          <t>256714</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>419863</t>
+          <t>419491</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>493701</t>
+          <t>493799</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>173321</t>
+          <t>176157</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>221758</t>
+          <t>221946</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>351995</t>
+          <t>355069</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>418077</t>
+          <t>415624</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>544710</t>
+          <t>540628</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>622898</t>
+          <t>623839</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>572477</t>
+          <t>571218</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>660005</t>
+          <t>660600</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>473056</t>
+          <t>472853</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>550928</t>
+          <t>554031</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1075805</t>
+          <t>1073898</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1189519</t>
+          <t>1191893</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>462148</t>
+          <t>465419</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>540385</t>
+          <t>548636</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>392254</t>
+          <t>392351</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>466177</t>
+          <t>467167</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>880718</t>
+          <t>878531</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>992295</t>
+          <t>986358</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>557170</t>
+          <t>559354</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>640416</t>
+          <t>642371</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>551530</t>
+          <t>555628</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>634239</t>
+          <t>640552</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1133157</t>
+          <t>1132174</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1255041</t>
+          <t>1250271</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>325245</t>
+          <t>324142</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>394070</t>
+          <t>391728</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>416332</t>
+          <t>410570</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>492101</t>
+          <t>487102</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>756741</t>
+          <t>758025</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>857813</t>
+          <t>864915</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>133113</t>
+          <t>133543</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>176928</t>
+          <t>176876</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>116290</t>
+          <t>116640</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157010</t>
+          <t>157309</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>262612</t>
+          <t>262035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>320040</t>
+          <t>324872</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>123794</t>
+          <t>125264</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>167322</t>
+          <t>169016</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>114714</t>
+          <t>115010</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>156882</t>
+          <t>155596</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>252293</t>
+          <t>252881</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>311929</t>
+          <t>308468</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139544</t>
+          <t>138176</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>183559</t>
+          <t>183434</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>145075</t>
+          <t>147515</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>192244</t>
+          <t>192638</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>298622</t>
+          <t>300372</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>364864</t>
+          <t>361503</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68540</t>
+          <t>67756</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104954</t>
+          <t>103322</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92457</t>
+          <t>92176</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129306</t>
+          <t>129840</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>169809</t>
+          <t>169008</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>219379</t>
+          <t>221253</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>906891</t>
+          <t>901697</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1017786</t>
+          <t>1010799</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>817839</t>
+          <t>817831</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>930322</t>
+          <t>924366</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1749749</t>
+          <t>1748792</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1901823</t>
+          <t>1902764</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>745033</t>
+          <t>744446</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>842145</t>
+          <t>842912</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>677531</t>
+          <t>676364</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>777676</t>
+          <t>776284</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1449960</t>
+          <t>1453893</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1594099</t>
+          <t>1594956</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>930345</t>
+          <t>932416</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1037603</t>
+          <t>1039761</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>935706</t>
+          <t>939440</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1046609</t>
+          <t>1042509</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1900209</t>
+          <t>1904670</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2061386</t>
+          <t>2060043</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,81%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>589727</t>
+          <t>594947</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>680803</t>
+          <t>682194</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>893884</t>
+          <t>893106</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1002706</t>
+          <t>1000121</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1510140</t>
+          <t>1518716</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1655647</t>
+          <t>1654743</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>131198</t>
+          <t>149692</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>114326</t>
+          <t>127937</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>151132</t>
+          <t>170929</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,32 +8284,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>165193</t>
+          <t>176894</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>148562</t>
+          <t>158298</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>185555</t>
+          <t>196550</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>296391</t>
+          <t>326586</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>273640</t>
+          <t>299228</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>325602</t>
+          <t>354666</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>114576</t>
+          <t>138156</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96606</t>
+          <t>119031</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131111</t>
+          <t>159443</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>118644</t>
+          <t>132901</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>104418</t>
+          <t>118071</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>134091</t>
+          <t>151062</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>233220</t>
+          <t>271057</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>212459</t>
+          <t>247755</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>257495</t>
+          <t>301865</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>123705</t>
+          <t>134228</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>105656</t>
+          <t>114455</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>143308</t>
+          <t>153560</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>167265</t>
+          <t>180798</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>150419</t>
+          <t>162635</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>184525</t>
+          <t>199245</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>290969</t>
+          <t>315026</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>265388</t>
+          <t>287688</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>316167</t>
+          <t>343845</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>140917</t>
+          <t>151513</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>133370</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>158964</t>
+          <t>172324</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>294454</t>
+          <t>320879</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>274644</t>
+          <t>298102</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>316576</t>
+          <t>341580</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>435370</t>
+          <t>472392</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>405065</t>
+          <t>443896</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>463790</t>
+          <t>500994</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>510396</t>
+          <t>573589</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>510396</t>
+          <t>573589</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>510396</t>
+          <t>573589</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>745556</t>
+          <t>811472</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>745556</t>
+          <t>811472</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>745556</t>
+          <t>811472</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1255951</t>
+          <t>1385061</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1255951</t>
+          <t>1385061</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1255951</t>
+          <t>1385061</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>720109</t>
+          <t>759963</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>482962</t>
+          <t>709466</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>825944</t>
+          <t>816326</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>583091</t>
+          <t>614177</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>434643</t>
+          <t>576367</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>684720</t>
+          <t>655861</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1303200</t>
+          <t>1374140</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1067288</t>
+          <t>1308336</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1461819</t>
+          <t>1445015</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,94%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>762558</t>
+          <t>573054</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>562805</t>
+          <t>523407</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1254564</t>
+          <t>621951</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>466899</t>
+          <t>527521</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>340907</t>
+          <t>488457</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>536207</t>
+          <t>568995</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1229457</t>
+          <t>1100574</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1005518</t>
+          <t>1046799</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1766830</t>
+          <t>1171595</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>435912</t>
+          <t>483548</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300356</t>
+          <t>443098</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>505036</t>
+          <t>530419</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>506844</t>
+          <t>489705</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>392999</t>
+          <t>454346</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>672411</t>
+          <t>526825</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>942755</t>
+          <t>973253</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>775704</t>
+          <t>917146</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1114692</t>
+          <t>1029421</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>362967</t>
+          <t>404403</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>252404</t>
+          <t>364985</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>426905</t>
+          <t>444640</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>675263</t>
+          <t>534017</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>503550</t>
+          <t>499300</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1105347</t>
+          <t>574290</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1038230</t>
+          <t>938421</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>841011</t>
+          <t>883130</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1663904</t>
+          <t>991606</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2281546</t>
+          <t>2220967</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2281546</t>
+          <t>2220967</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2281546</t>
+          <t>2220967</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2232096</t>
+          <t>2165420</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2232096</t>
+          <t>2165420</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2232096</t>
+          <t>2165420</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4513642</t>
+          <t>4386388</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4513642</t>
+          <t>4386388</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4513642</t>
+          <t>4386388</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>206588</t>
+          <t>227459</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>181037</t>
+          <t>203264</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>234246</t>
+          <t>257837</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>180476</t>
+          <t>196481</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>161861</t>
+          <t>174904</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>202965</t>
+          <t>218342</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>387064</t>
+          <t>423940</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>357361</t>
+          <t>391406</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>423107</t>
+          <t>459016</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>173040</t>
+          <t>188523</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>149842</t>
+          <t>163887</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>200049</t>
+          <t>213468</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>162833</t>
+          <t>177056</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>143155</t>
+          <t>158306</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181283</t>
+          <t>199197</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>335874</t>
+          <t>365578</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>304001</t>
+          <t>333962</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>367007</t>
+          <t>399202</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>138523</t>
+          <t>161337</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>117237</t>
+          <t>138958</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>158263</t>
+          <t>185960</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>158999</t>
+          <t>182725</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>140278</t>
+          <t>162621</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>177170</t>
+          <t>204181</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>297522</t>
+          <t>344061</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>271153</t>
+          <t>315637</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>331181</t>
+          <t>375687</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -9726,32 +9726,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>126309</t>
+          <t>131816</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105665</t>
+          <t>111352</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>158954</t>
+          <t>154992</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>155280</t>
+          <t>175529</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135953</t>
+          <t>158066</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174573</t>
+          <t>196128</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>281589</t>
+          <t>307345</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>251187</t>
+          <t>277120</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>314116</t>
+          <t>337388</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>644461</t>
+          <t>709134</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>644461</t>
+          <t>709134</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>644461</t>
+          <t>709134</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>657589</t>
+          <t>731791</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>657589</t>
+          <t>731791</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>657589</t>
+          <t>731791</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1302050</t>
+          <t>1440925</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1302050</t>
+          <t>1440925</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1302050</t>
+          <t>1440925</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1057895</t>
+          <t>1137114</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>1071119</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1163278</t>
+          <t>1198957</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>928760</t>
+          <t>987552</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>767965</t>
+          <t>936965</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1022377</t>
+          <t>1036532</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1986655</t>
+          <t>2124666</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1712828</t>
+          <t>2048931</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2139365</t>
+          <t>2201315</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1050175</t>
+          <t>899732</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>846984</t>
+          <t>843399</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1624791</t>
+          <t>955751</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>748376</t>
+          <t>837478</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>603633</t>
+          <t>791785</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>816437</t>
+          <t>886014</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1798551</t>
+          <t>1737210</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1565431</t>
+          <t>1665816</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2388231</t>
+          <t>1810331</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>698140</t>
+          <t>779113</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>552828</t>
+          <t>724206</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>772338</t>
+          <t>830969</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>833107</t>
+          <t>853227</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>700070</t>
+          <t>798515</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>980813</t>
+          <t>896126</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1531247</t>
+          <t>1632340</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1339952</t>
+          <t>1563558</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1715907</t>
+          <t>1707548</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>630193</t>
+          <t>687732</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>502703</t>
+          <t>644460</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>701798</t>
+          <t>740242</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1124997</t>
+          <t>1030426</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>962254</t>
+          <t>984460</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1580570</t>
+          <t>1079058</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1755189</t>
+          <t>1718158</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1543718</t>
+          <t>1653159</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2406317</t>
+          <t>1787059</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3436403</t>
+          <t>3503691</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3436403</t>
+          <t>3503691</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3436403</t>
+          <t>3503691</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3635240</t>
+          <t>3708683</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3635240</t>
+          <t>3708683</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3635240</t>
+          <t>3708683</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7071643</t>
+          <t>7212374</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7071643</t>
+          <t>7212374</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7071643</t>
+          <t>7212374</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
